--- a/2-file/not_pay.xlsx
+++ b/2-file/not_pay.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -48,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -425,8 +422,10 @@
           <t>OD20260601002</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n">
-        <v>46174</v>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
@@ -435,252 +434,191 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>机械键盘</t>
-        </is>
-      </c>
-      <c r="F1" t="n">
+          <t>未付款</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>鼠标</t>
+        </is>
+      </c>
+      <c r="G1" t="n">
         <v>1</v>
       </c>
-      <c r="G1" t="n">
-        <v>299</v>
-      </c>
       <c r="H1" t="n">
-        <v>299</v>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>未付款</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>提醒付款</t>
-        </is>
+        <v>89</v>
+      </c>
+      <c r="I1" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OD20260601004</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>46175</v>
+          <t>OD20260601005</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>陈雪</t>
+          <t>陈晨</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>蓝牙耳机</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
+          <t>未付款</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>移动硬盘</t>
+        </is>
       </c>
       <c r="G2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>387</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>未付款</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>大客户</t>
-        </is>
+        <v>459</v>
+      </c>
+      <c r="I2" t="n">
+        <v>459</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OD20260601006</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>46176</v>
+          <t>OD20260601009</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>孙婷</t>
+          <t>孙浩</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>西北</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>笔记本支架</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>4</v>
+          <t>未付款</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>U盘</t>
+        </is>
       </c>
       <c r="G3" t="n">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>316</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>未付款</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>电话确认</t>
-        </is>
+        <v>39.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>199.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OD20260601008</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>46177</v>
+          <t>OD20260601013</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>吴然</t>
+          <t>林欣</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>数据线</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>8</v>
+          <t>未付款</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>充电器</t>
+        </is>
       </c>
       <c r="G4" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>152</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>未付款</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>小额订单</t>
-        </is>
+        <v>69</v>
+      </c>
+      <c r="I4" t="n">
+        <v>207</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OD20260601010</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>46178</v>
+          <t>OD20260601017</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>刘洋</t>
+          <t>曹婷</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>西安</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>路由器</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
+          <t>未付款</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>鼠标垫</t>
+        </is>
       </c>
       <c r="G5" t="n">
-        <v>239</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>239</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>未付款</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>等待转账</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>OD20260601012</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>46179</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>何苗</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>平板保护套</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>39</v>
-      </c>
-      <c r="H6" t="n">
-        <v>234</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>未付款</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>批量采购</t>
-        </is>
+        <v>19.9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>119.4</v>
       </c>
     </row>
   </sheetData>
